--- a/egs2/lrac2/track1/LRAC2-Track1-VoCodec-Model-Design-Sheet.xlsx
+++ b/egs2/lrac2/track1/LRAC2-Track1-VoCodec-Model-Design-Sheet.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary-Track1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Encoder-Track1'!$A$17:$V$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decoder-Track1'!$A$17:$V$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Encoder-Track1'!$A$19:$V$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decoder-Track1'!$A$19:$V$36</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -232,89 +232,94 @@
     <author>LRAC 2</author>
   </authors>
   <commentList>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
+    <comment ref="L21" authorId="0" shapeId="0">
       <text>
         <t>Includes Encoder input LayerNorm scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="L22" authorId="0" shapeId="0">
       <text>
         <t>Includes ConvNeXt LayerNorm scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L23" authorId="0" shapeId="0">
+    <comment ref="L25" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm1 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S25" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L24" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm2 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L25" authorId="0" shapeId="0">
+    <comment ref="L27" authorId="0" shapeId="0">
       <text>
         <t>Includes Attention input LayerNorm scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S28" authorId="0" shapeId="0">
+      <text>
+        <t>The inverse-frequency vector is derived rather than learned and does not count toward the parameter cap. It is read once per attention invocation; the generated sine/cosine values are retained and reused for both query and key rotation.</t>
+      </text>
+    </comment>
+    <comment ref="S31" authorId="0" shapeId="0">
       <text>
         <t>The first term reads the key cache for the previous/lookahead frames; the second writes the current key. Attention context includes the current frame.</t>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S32" authorId="0" shapeId="0">
       <text>
         <t>The first term reads the value cache for the previous/lookahead frames; the second writes the current value. Attention context includes the current frame.</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L34" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm1 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S34" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L30" authorId="0" shapeId="0">
+    <comment ref="L35" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm2 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S30" authorId="0" shapeId="0">
+    <comment ref="S35" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
+    <comment ref="L36" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet output LayerNorm scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
+    <comment ref="S36" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
   </commentList>
@@ -327,82 +332,87 @@
     <author>LRAC 2</author>
   </authors>
   <commentList>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="L22" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm1 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
+    <comment ref="L23" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm2 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S23" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L22" authorId="0" shapeId="0">
+    <comment ref="L24" authorId="0" shapeId="0">
       <text>
         <t>Includes Attention input LayerNorm scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S25" authorId="0" shapeId="0">
+      <text>
+        <t>The inverse-frequency vector is derived rather than learned and does not count toward the parameter cap. It is read once per attention invocation; the generated sine/cosine values are retained and reused for both query and key rotation.</t>
+      </text>
+    </comment>
+    <comment ref="S28" authorId="0" shapeId="0">
       <text>
         <t>The first term reads the key cache for the previous/lookahead frames; the second writes the current key. Attention context includes the current frame.</t>
       </text>
     </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <t>The first term reads the value cache for the previous/lookahead frames; the second writes the current value. Attention context includes the current frame.</t>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L31" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm1 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S31" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L27" authorId="0" shapeId="0">
+    <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet residual-block norm2 scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S32" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>Includes ConvNeXt LayerNorm scale and bias. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
-        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B15 and B16.</t>
+        <t>The first term reads the runtime state and the second term writes it. The access counts come from cells B17 and B18.</t>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
+    <comment ref="L36" authorId="0" shapeId="0">
       <text>
         <t>Includes PosNet output LayerNorm and decoder output LayerNorm scales and biases. The additive term in this formula is 2 × model channels per LayerNorm.</t>
       </text>
@@ -700,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -730,7 +740,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VoCodec Encoder — 100 Hz / 32-layer</t>
+          <t>VoCodec Encoder — 100 Hz / 24-layer / RoPE</t>
         </is>
       </c>
     </row>
@@ -745,7 +755,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Computations only include MAC-bearing operations. The first STFT/ISTFT row has zero counted MACs but explicitly accounts for its persistent window and streaming overlap state. LayerNorm arithmetic is omitted, while each LayerNorm's scale and bias values are included in column L through the +2*$B$6 terms; +4*$B$6 includes two LayerNorms. Hover over those cells for the exact association. Activations, residual additions, dropout, softmax, and FFT arithmetic are omitted under the LRAC sheet convention. Overall Stride in B5 drives compute, field-of-view, and memory-bandwidth formulas. Channel dimensions are centralized in B6:B9, and bounded attention settings are centralized in B10:B12. Bytes per value and runtime state read/write assumptions are centralized in B14:B16. The layer table references those cells. All totals derive only from visible formulas.</t>
+          <t>Computations only include MAC-bearing operations. The first STFT/ISTFT row has zero counted MACs but explicitly accounts for its persistent window and streaming overlap state. LayerNorm arithmetic is omitted, while each LayerNorm's scale and bias values are included in column L through the +2*$B$6 terms; +4*$B$6 includes two LayerNorms. Hover over those cells for the exact association. Activations, residual additions, dropout, softmax, and FFT arithmetic are omitted under the LRAC sheet convention. Overall Stride in B5 drives compute, field-of-view, and memory-bandwidth formulas. Channel dimensions are centralized in B6:B9, and bounded attention and RoPE settings are centralized in B10:B14. Bytes per value and runtime state read/write assumptions are centralized in B16:B18. The layer table references those cells. All totals derive only from visible formulas.</t>
         </is>
       </c>
     </row>
@@ -787,7 +797,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -855,381 +865,227 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>STFT buffering latency (ms)</t>
-        </is>
-      </c>
-      <c r="B13" s="3">
-        <f>$B$4/$B$2*1000</f>
-        <v/>
+          <t>Attention uses RoPE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bytes per parameter/buffer value</t>
+          <t>RoPE rotary dimensions / head</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Runtime state reads per call</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
+          <t>STFT buffering latency (ms)</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>$B$4/$B$2*1000</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Bytes per parameter/buffer value</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Runtime state reads per call</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Runtime state writes per call</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Layer Name</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Block ID</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t># Blocks</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Operation</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Kernel / Context</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Dilation</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Input Channels</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Output Channels</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Groups / Heads</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>MAC / Position / Block</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>MMAC/s</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Trainable Params / Block</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Total Trainable Params</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>FOV Left / Block</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>FOV Right / Block</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Total FOV Left (ms)</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Latency (ms)</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>Parameter-Cap Values / Block</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>Runtime State/Cache Accesses (R+W) / Call / Block</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>Model-Params BW Total (MB/s)</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>State/Cache BW Total (MB/s)</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>Total BW (MB/s)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>STFT analysis window and overlap state</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>STFT analysis</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="C20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Persistent window and streaming state; FFT MACs excluded</t>
         </is>
       </c>
-      <c r="E18" s="6">
+      <c r="E20" s="6">
         <f>$B$3</f>
         <v/>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="8">
-        <f>C18*$B$5*J18/10^6</f>
-        <v/>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7">
-        <f>C18*L18</f>
-        <v/>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="8">
-        <f>C18*N18/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q18" s="8">
-        <f>C18*O18/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R18" s="7">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="S18" s="7">
-        <f>$B$15*($B$3-$B$4)+$B$16*($B$3-$B$4)</f>
-        <v/>
-      </c>
-      <c r="T18" s="8">
-        <f>C18*$B$5*$B$14*R18/10^6</f>
-        <v/>
-      </c>
-      <c r="U18" s="8">
-        <f>C18*$B$5*$B$14*S18/10^6</f>
-        <v/>
-      </c>
-      <c r="V18" s="8">
-        <f>SUM(T18:U18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>STFT feature projection</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Encoder input</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Conv1d / linear projection</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="9">
-        <f>$B$9</f>
-        <v/>
-      </c>
-      <c r="H19" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="10">
-        <f>E19*G19*H19/I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="11">
-        <f>C19*$B$5*J19/10^6</f>
-        <v/>
-      </c>
-      <c r="L19" s="10">
-        <f>J19+H19+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M19" s="10">
-        <f>C19*L19</f>
-        <v/>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="11">
-        <f>C19*N19/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q19" s="11">
-        <f>C19*O19/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R19" s="10">
-        <f>L19</f>
-        <v/>
-      </c>
-      <c r="S19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="11">
-        <f>C19*$B$5*$B$14*R19/10^6</f>
-        <v/>
-      </c>
-      <c r="U19" s="11">
-        <f>C19*$B$5*$B$14*S19/10^6</f>
-        <v/>
-      </c>
-      <c r="V19" s="11">
-        <f>SUM(T19:U19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" outlineLevel="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Depthwise convolution</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>ConvNeXt blocks 1–6</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="F20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H20" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I20" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="J20" s="7">
-        <f>E20*G20*H20/I20</f>
-        <v/>
+      <c r="G20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="8">
         <f>C20*$B$5*J20/10^6</f>
         <v/>
       </c>
-      <c r="L20" s="7">
-        <f>J20+H20+2*$B$6</f>
-        <v/>
+      <c r="L20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="7">
         <f>C20*L20</f>
         <v/>
       </c>
       <c r="N20" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>0</v>
@@ -1243,19 +1099,19 @@
         <v/>
       </c>
       <c r="R20" s="7">
-        <f>L20</f>
+        <f>$B$3</f>
         <v/>
       </c>
       <c r="S20" s="7">
-        <f>$B$15*(E20-1)*F20*G20+$B$16*(E20-1)*F20*G20</f>
+        <f>$B$17*($B$3-$B$4)+$B$18*($B$3-$B$4)</f>
         <v/>
       </c>
       <c r="T20" s="8">
-        <f>C20*$B$5*$B$14*R20/10^6</f>
+        <f>C20*$B$5*$B$16*R20/10^6</f>
         <v/>
       </c>
       <c r="U20" s="8">
-        <f>C20*$B$5*$B$14*S20/10^6</f>
+        <f>C20*$B$5*$B$16*S20/10^6</f>
         <v/>
       </c>
       <c r="V20" s="8">
@@ -1263,88 +1119,88 @@
         <v/>
       </c>
     </row>
-    <row r="21" outlineLevel="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Pointwise input projection</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>ConvNeXt blocks 1–6</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>STFT feature projection</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Encoder input</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Conv1d / linear projection</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H21" s="6">
-        <f>$B$7</f>
-        <v/>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="7">
+      <c r="E21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10">
         <f>E21*G21*H21/I21</f>
         <v/>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="11">
         <f>C21*$B$5*J21/10^6</f>
         <v/>
       </c>
-      <c r="L21" s="7">
-        <f>J21+H21+0</f>
-        <v/>
-      </c>
-      <c r="M21" s="7">
+      <c r="L21" s="10">
+        <f>J21+H21+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M21" s="10">
         <f>C21*L21</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8">
+      <c r="N21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="11">
         <f>C21*N21/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="11">
         <f>C21*O21/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R21" s="7">
+      <c r="R21" s="10">
         <f>L21</f>
         <v/>
       </c>
-      <c r="S21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8">
-        <f>C21*$B$5*$B$14*R21/10^6</f>
-        <v/>
-      </c>
-      <c r="U21" s="8">
-        <f>C21*$B$5*$B$14*S21/10^6</f>
-        <v/>
-      </c>
-      <c r="V21" s="8">
+      <c r="S21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="11">
+        <f>C21*$B$5*$B$16*R21/10^6</f>
+        <v/>
+      </c>
+      <c r="U21" s="11">
+        <f>C21*$B$5*$B$16*S21/10^6</f>
+        <v/>
+      </c>
+      <c r="V21" s="11">
         <f>SUM(T21:U21)</f>
         <v/>
       </c>
@@ -1352,7 +1208,7 @@
     <row r="22" outlineLevel="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Pointwise output projection</t>
+          <t>Depthwise convolution</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1365,25 +1221,26 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Conv1d / linear projection</t>
+          <t>Causal Conv1d</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="6">
-        <f>$B$7</f>
+        <f>$B$6</f>
         <v/>
       </c>
       <c r="H22" s="6">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
+      <c r="I22" s="6">
+        <f>$B$6</f>
+        <v/>
       </c>
       <c r="J22" s="7">
         <f>E22*G22*H22/I22</f>
@@ -1394,7 +1251,7 @@
         <v/>
       </c>
       <c r="L22" s="7">
-        <f>J22+H22+0</f>
+        <f>J22+H22+2*$B$6</f>
         <v/>
       </c>
       <c r="M22" s="7">
@@ -1402,7 +1259,7 @@
         <v/>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0</v>
@@ -1419,15 +1276,16 @@
         <f>L22</f>
         <v/>
       </c>
-      <c r="S22" s="7" t="n">
-        <v>0</v>
+      <c r="S22" s="7">
+        <f>$B$17*(E22-1)*F22*G22+$B$18*(E22-1)*F22*G22</f>
+        <v/>
       </c>
       <c r="T22" s="8">
-        <f>C22*$B$5*$B$14*R22/10^6</f>
+        <f>C22*$B$5*$B$16*R22/10^6</f>
         <v/>
       </c>
       <c r="U22" s="8">
-        <f>C22*$B$5*$B$14*S22/10^6</f>
+        <f>C22*$B$5*$B$16*S22/10^6</f>
         <v/>
       </c>
       <c r="V22" s="8">
@@ -1436,350 +1294,347 @@
       </c>
     </row>
     <row r="23" outlineLevel="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Pointwise input projection</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ConvNeXt blocks 1–6</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H23" s="6">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7">
+        <f>E23*G23*H23/I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="8">
+        <f>C23*$B$5*J23/10^6</f>
+        <v/>
+      </c>
+      <c r="L23" s="7">
+        <f>J23+H23+0</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>C23*L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8">
+        <f>C23*N23/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q23" s="8">
+        <f>C23*O23/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R23" s="7">
+        <f>L23</f>
+        <v/>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="8">
+        <f>C23*$B$5*$B$16*R23/10^6</f>
+        <v/>
+      </c>
+      <c r="U23" s="8">
+        <f>C23*$B$5*$B$16*S23/10^6</f>
+        <v/>
+      </c>
+      <c r="V23" s="8">
+        <f>SUM(T23:U23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Pointwise output projection</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>ConvNeXt blocks 1–6</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="H24" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7">
+        <f>E24*G24*H24/I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="8">
+        <f>C24*$B$5*J24/10^6</f>
+        <v/>
+      </c>
+      <c r="L24" s="7">
+        <f>J24+H24+0</f>
+        <v/>
+      </c>
+      <c r="M24" s="7">
+        <f>C24*L24</f>
+        <v/>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8">
+        <f>C24*N24/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q24" s="8">
+        <f>C24*O24/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R24" s="7">
+        <f>L24</f>
+        <v/>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="8">
+        <f>C24*$B$5*$B$16*R24/10^6</f>
+        <v/>
+      </c>
+      <c r="U24" s="8">
+        <f>C24*$B$5*$B$16*S24/10^6</f>
+        <v/>
+      </c>
+      <c r="V24" s="8">
+        <f>SUM(T24:U24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Residual convolution 1</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>PosNet ResNet blocks 1–2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Causal Conv1d</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="10">
-        <f>E23*G23*H23/I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="11">
-        <f>C23*$B$5*J23/10^6</f>
-        <v/>
-      </c>
-      <c r="L23" s="10">
-        <f>J23+H23+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M23" s="10">
-        <f>C23*L23</f>
-        <v/>
-      </c>
-      <c r="N23" s="9" t="n">
+      <c r="F25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10">
+        <f>E25*G25*H25/I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="11">
+        <f>C25*$B$5*J25/10^6</f>
+        <v/>
+      </c>
+      <c r="L25" s="10">
+        <f>J25+H25+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M25" s="10">
+        <f>C25*L25</f>
+        <v/>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="11">
-        <f>C23*N23/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q23" s="11">
-        <f>C23*O23/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R23" s="10">
-        <f>L23</f>
-        <v/>
-      </c>
-      <c r="S23" s="10">
-        <f>$B$15*(E23-1)*F23*G23+$B$16*(E23-1)*F23*G23</f>
-        <v/>
-      </c>
-      <c r="T23" s="11">
-        <f>C23*$B$5*$B$14*R23/10^6</f>
-        <v/>
-      </c>
-      <c r="U23" s="11">
-        <f>C23*$B$5*$B$14*S23/10^6</f>
-        <v/>
-      </c>
-      <c r="V23" s="11">
-        <f>SUM(T23:U23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="O25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="11">
+        <f>C25*N25/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q25" s="11">
+        <f>C25*O25/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R25" s="10">
+        <f>L25</f>
+        <v/>
+      </c>
+      <c r="S25" s="10">
+        <f>$B$17*(E25-1)*F25*G25+$B$18*(E25-1)*F25*G25</f>
+        <v/>
+      </c>
+      <c r="T25" s="11">
+        <f>C25*$B$5*$B$16*R25/10^6</f>
+        <v/>
+      </c>
+      <c r="U25" s="11">
+        <f>C25*$B$5*$B$16*S25/10^6</f>
+        <v/>
+      </c>
+      <c r="V25" s="11">
+        <f>SUM(T25:U25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" outlineLevel="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Residual convolution 2</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>PosNet ResNet blocks 1–2</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Causal Conv1d</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H24" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="10">
-        <f>E24*G24*H24/I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="11">
-        <f>C24*$B$5*J24/10^6</f>
-        <v/>
-      </c>
-      <c r="L24" s="10">
-        <f>J24+H24+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M24" s="10">
-        <f>C24*L24</f>
-        <v/>
-      </c>
-      <c r="N24" s="9" t="n">
+      <c r="F26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10">
+        <f>E26*G26*H26/I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="11">
+        <f>C26*$B$5*J26/10^6</f>
+        <v/>
+      </c>
+      <c r="L26" s="10">
+        <f>J26+H26+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M26" s="10">
+        <f>C26*L26</f>
+        <v/>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="11">
-        <f>C24*N24/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q24" s="11">
-        <f>C24*O24/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R24" s="10">
-        <f>L24</f>
-        <v/>
-      </c>
-      <c r="S24" s="10">
-        <f>$B$15*(E24-1)*F24*G24+$B$16*(E24-1)*F24*G24</f>
-        <v/>
-      </c>
-      <c r="T24" s="11">
-        <f>C24*$B$5*$B$14*R24/10^6</f>
-        <v/>
-      </c>
-      <c r="U24" s="11">
-        <f>C24*$B$5*$B$14*S24/10^6</f>
-        <v/>
-      </c>
-      <c r="V24" s="11">
-        <f>SUM(T24:U24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>QKV projection</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Bounded attention after PosNet block 2</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Conv1d / linear projection</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H25" s="6">
-        <f>$B$8</f>
-        <v/>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="7">
-        <f>E25*G25*H25/I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="8">
-        <f>C25*$B$5*J25/10^6</f>
-        <v/>
-      </c>
-      <c r="L25" s="7">
-        <f>J25+H25+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M25" s="7">
-        <f>C25*L25</f>
-        <v/>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8">
-        <f>C25*N25/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q25" s="8">
-        <f>C25*O25/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R25" s="7">
-        <f>L25</f>
-        <v/>
-      </c>
-      <c r="S25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="8">
-        <f>C25*$B$5*$B$14*R25/10^6</f>
-        <v/>
-      </c>
-      <c r="U25" s="8">
-        <f>C25*$B$5*$B$14*S25/10^6</f>
-        <v/>
-      </c>
-      <c r="V25" s="8">
-        <f>SUM(T25:U25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Query-key score product</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Bounded attention after PosNet block 2</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Q × Kᵀ (configured bounded context)</t>
-        </is>
-      </c>
-      <c r="E26" s="6">
-        <f>$B$10+$B$11</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H26" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I26" s="6">
-        <f>$B$12</f>
-        <v/>
-      </c>
-      <c r="J26" s="7">
-        <f>I26*E26*(G26/I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="8">
-        <f>C26*$B$5*J26/10^6</f>
-        <v/>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7">
-        <f>C26*L26</f>
-        <v/>
-      </c>
-      <c r="N26" s="6">
-        <f>$B$10-1</f>
-        <v/>
-      </c>
-      <c r="O26" s="6">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="P26" s="8">
+      <c r="O26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="11">
         <f>C26*N26/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q26" s="8">
+      <c r="Q26" s="11">
         <f>C26*O26/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="7">
-        <f>$B$15*($B$10-1+$B$11)*G26+$B$16*G26</f>
-        <v/>
-      </c>
-      <c r="T26" s="8">
-        <f>C26*$B$5*$B$14*R26/10^6</f>
-        <v/>
-      </c>
-      <c r="U26" s="8">
-        <f>C26*$B$5*$B$14*S26/10^6</f>
-        <v/>
-      </c>
-      <c r="V26" s="8">
+      <c r="R26" s="10">
+        <f>L26</f>
+        <v/>
+      </c>
+      <c r="S26" s="10">
+        <f>$B$17*(E26-1)*F26*G26+$B$18*(E26-1)*F26*G26</f>
+        <v/>
+      </c>
+      <c r="T26" s="11">
+        <f>C26*$B$5*$B$16*R26/10^6</f>
+        <v/>
+      </c>
+      <c r="U26" s="11">
+        <f>C26*$B$5*$B$16*S26/10^6</f>
+        <v/>
+      </c>
+      <c r="V26" s="11">
         <f>SUM(T26:U26)</f>
         <v/>
       </c>
@@ -1787,7 +1642,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Attention-weighted value product</t>
+          <t>QKV projection</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1800,12 +1655,11 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>softmax(QKᵀ) × V</t>
-        </is>
-      </c>
-      <c r="E27" s="6">
-        <f>$B$10+$B$11</f>
-        <v/>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>1</v>
@@ -1815,23 +1669,23 @@
         <v/>
       </c>
       <c r="H27" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I27" s="6">
-        <f>$B$12</f>
-        <v/>
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="7">
-        <f>I27*E27*(G27/I27)</f>
+        <f>E27*G27*H27/I27</f>
         <v/>
       </c>
       <c r="K27" s="8">
         <f>C27*$B$5*J27/10^6</f>
         <v/>
       </c>
-      <c r="L27" s="7" t="n">
-        <v>0</v>
+      <c r="L27" s="7">
+        <f>J27+H27+2*$B$6</f>
+        <v/>
       </c>
       <c r="M27" s="7">
         <f>C27*L27</f>
@@ -1851,19 +1705,19 @@
         <f>C27*O27/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="7">
-        <f>$B$15*($B$10-1+$B$11)*G27+$B$16*G27</f>
-        <v/>
+      <c r="R27" s="7">
+        <f>L27</f>
+        <v/>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T27" s="8">
-        <f>C27*$B$5*$B$14*R27/10^6</f>
+        <f>C27*$B$5*$B$16*R27/10^6</f>
         <v/>
       </c>
       <c r="U27" s="8">
-        <f>C27*$B$5*$B$14*S27/10^6</f>
+        <f>C27*$B$5*$B$16*S27/10^6</f>
         <v/>
       </c>
       <c r="V27" s="8">
@@ -1874,7 +1728,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Attention output projection</t>
+          <t>RoPE phase generation</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1887,11 +1741,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Conv1d / linear projection</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>1</v>
+          <t>Position × derived inverse frequencies; sine/cosine arithmetic excluded</t>
+        </is>
+      </c>
+      <c r="E28" s="6">
+        <f>$B$14/2</f>
+        <v/>
       </c>
       <c r="F28" s="6" t="n">
         <v>1</v>
@@ -1908,16 +1763,15 @@
         <v>1</v>
       </c>
       <c r="J28" s="7">
-        <f>E28*G28*H28/I28</f>
+        <f>E28</f>
         <v/>
       </c>
       <c r="K28" s="8">
         <f>C28*$B$5*J28/10^6</f>
         <v/>
       </c>
-      <c r="L28" s="7">
-        <f>J28+H28+0</f>
-        <v/>
+      <c r="L28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="7">
         <f>C28*L28</f>
@@ -1937,19 +1791,19 @@
         <f>C28*O28/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R28" s="7">
-        <f>L28</f>
-        <v/>
-      </c>
-      <c r="S28" s="7" t="n">
-        <v>0</v>
+      <c r="R28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="7">
+        <f>$B$17*($B$14/2)</f>
+        <v/>
       </c>
       <c r="T28" s="8">
-        <f>C28*$B$5*$B$14*R28/10^6</f>
+        <f>C28*$B$5*$B$16*R28/10^6</f>
         <v/>
       </c>
       <c r="U28" s="8">
-        <f>C28*$B$5*$B$14*S28/10^6</f>
+        <f>C28*$B$5*$B$16*S28/10^6</f>
         <v/>
       </c>
       <c r="V28" s="8">
@@ -1957,176 +1811,174 @@
         <v/>
       </c>
     </row>
-    <row r="29" outlineLevel="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Residual convolution 1</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>PosNet ResNet blocks 3–4</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H29" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="10">
-        <f>E29*G29*H29/I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="11">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>RoPE query rotation</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Bounded attention after PosNet block 2</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Pairwise rotary transform of Q</t>
+        </is>
+      </c>
+      <c r="E29" s="6">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H29" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I29" s="6">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="J29" s="7">
+        <f>2*E29*I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="8">
         <f>C29*$B$5*J29/10^6</f>
         <v/>
       </c>
-      <c r="L29" s="10">
-        <f>J29+H29+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M29" s="10">
+      <c r="L29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7">
         <f>C29*L29</f>
         <v/>
       </c>
-      <c r="N29" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="11">
+      <c r="N29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8">
         <f>C29*N29/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q29" s="11">
+      <c r="Q29" s="8">
         <f>C29*O29/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R29" s="10">
-        <f>L29</f>
-        <v/>
-      </c>
-      <c r="S29" s="10">
-        <f>$B$15*(E29-1)*F29*G29+$B$16*(E29-1)*F29*G29</f>
-        <v/>
-      </c>
-      <c r="T29" s="11">
-        <f>C29*$B$5*$B$14*R29/10^6</f>
-        <v/>
-      </c>
-      <c r="U29" s="11">
-        <f>C29*$B$5*$B$14*S29/10^6</f>
-        <v/>
-      </c>
-      <c r="V29" s="11">
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="8">
+        <f>C29*$B$5*$B$16*R29/10^6</f>
+        <v/>
+      </c>
+      <c r="U29" s="8">
+        <f>C29*$B$5*$B$16*S29/10^6</f>
+        <v/>
+      </c>
+      <c r="V29" s="8">
         <f>SUM(T29:U29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" outlineLevel="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Residual convolution 2</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>PosNet ResNet blocks 3–4</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H30" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="10">
-        <f>E30*G30*H30/I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="11">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>RoPE key rotation</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Bounded attention after PosNet block 2</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Pairwise rotary transform of K before cache use</t>
+        </is>
+      </c>
+      <c r="E30" s="6">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H30" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I30" s="6">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="J30" s="7">
+        <f>2*E30*I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="8">
         <f>C30*$B$5*J30/10^6</f>
         <v/>
       </c>
-      <c r="L30" s="10">
-        <f>J30+H30+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M30" s="10">
+      <c r="L30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7">
         <f>C30*L30</f>
         <v/>
       </c>
-      <c r="N30" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="11">
+      <c r="N30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8">
         <f>C30*N30/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q30" s="11">
+      <c r="Q30" s="8">
         <f>C30*O30/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R30" s="10">
-        <f>L30</f>
-        <v/>
-      </c>
-      <c r="S30" s="10">
-        <f>$B$15*(E30-1)*F30*G30+$B$16*(E30-1)*F30*G30</f>
-        <v/>
-      </c>
-      <c r="T30" s="11">
-        <f>C30*$B$5*$B$14*R30/10^6</f>
-        <v/>
-      </c>
-      <c r="U30" s="11">
-        <f>C30*$B$5*$B$14*S30/10^6</f>
-        <v/>
-      </c>
-      <c r="V30" s="11">
+      <c r="R30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="8">
+        <f>C30*$B$5*$B$16*R30/10^6</f>
+        <v/>
+      </c>
+      <c r="U30" s="8">
+        <f>C30*$B$5*$B$16*S30/10^6</f>
+        <v/>
+      </c>
+      <c r="V30" s="8">
         <f>SUM(T30:U30)</f>
         <v/>
       </c>
@@ -2134,12 +1986,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Latent projection</t>
+          <t>Query-key score product</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Encoder output</t>
+          <t>Bounded attention after PosNet block 2</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -2147,11 +1999,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>3</v>
+          <t>Q × Kᵀ (configured bounded context)</t>
+        </is>
+      </c>
+      <c r="E31" s="6">
+        <f>$B$10+$B$11</f>
+        <v/>
       </c>
       <c r="F31" s="6" t="n">
         <v>1</v>
@@ -2164,30 +2017,32 @@
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>1</v>
+      <c r="I31" s="6">
+        <f>$B$12</f>
+        <v/>
       </c>
       <c r="J31" s="7">
-        <f>E31*G31*H31/I31</f>
+        <f>I31*E31*(G31/I31)</f>
         <v/>
       </c>
       <c r="K31" s="8">
         <f>C31*$B$5*J31/10^6</f>
         <v/>
       </c>
-      <c r="L31" s="7">
-        <f>J31+H31+2*$B$6</f>
-        <v/>
+      <c r="L31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="7">
         <f>C31*L31</f>
         <v/>
       </c>
-      <c r="N31" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O31" s="6" t="n">
-        <v>0</v>
+      <c r="N31" s="6">
+        <f>$B$10-1</f>
+        <v/>
+      </c>
+      <c r="O31" s="6">
+        <f>$B$11</f>
+        <v/>
       </c>
       <c r="P31" s="8">
         <f>C31*N31/$B$5*1000</f>
@@ -2197,20 +2052,19 @@
         <f>C31*O31/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R31" s="7">
-        <f>L31</f>
-        <v/>
+      <c r="R31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="S31" s="7">
-        <f>$B$15*(E31-1)*F31*G31+$B$16*(E31-1)*F31*G31</f>
+        <f>$B$17*($B$10-1+$B$11)*G31+$B$18*G31</f>
         <v/>
       </c>
       <c r="T31" s="8">
-        <f>C31*$B$5*$B$14*R31/10^6</f>
+        <f>C31*$B$5*$B$16*R31/10^6</f>
         <v/>
       </c>
       <c r="U31" s="8">
-        <f>C31*$B$5*$B$14*S31/10^6</f>
+        <f>C31*$B$5*$B$16*S31/10^6</f>
         <v/>
       </c>
       <c r="V31" s="8">
@@ -2219,102 +2073,536 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Attention-weighted value product</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Bounded attention after PosNet block 2</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>softmax(QKᵀ) × V</t>
+        </is>
+      </c>
+      <c r="E32" s="6">
+        <f>$B$10+$B$11</f>
+        <v/>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H32" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I32" s="6">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="J32" s="7">
+        <f>I32*E32*(G32/I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="8">
+        <f>C32*$B$5*J32/10^6</f>
+        <v/>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7">
+        <f>C32*L32</f>
+        <v/>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <f>C32*N32/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q32" s="8">
+        <f>C32*O32/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="7">
+        <f>$B$17*($B$10-1+$B$11)*G32+$B$18*G32</f>
+        <v/>
+      </c>
+      <c r="T32" s="8">
+        <f>C32*$B$5*$B$16*R32/10^6</f>
+        <v/>
+      </c>
+      <c r="U32" s="8">
+        <f>C32*$B$5*$B$16*S32/10^6</f>
+        <v/>
+      </c>
+      <c r="V32" s="8">
+        <f>SUM(T32:U32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Attention output projection</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Bounded attention after PosNet block 2</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H33" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
+        <f>E33*G33*H33/I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="8">
+        <f>C33*$B$5*J33/10^6</f>
+        <v/>
+      </c>
+      <c r="L33" s="7">
+        <f>J33+H33+0</f>
+        <v/>
+      </c>
+      <c r="M33" s="7">
+        <f>C33*L33</f>
+        <v/>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8">
+        <f>C33*N33/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q33" s="8">
+        <f>C33*O33/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R33" s="7">
+        <f>L33</f>
+        <v/>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="8">
+        <f>C33*$B$5*$B$16*R33/10^6</f>
+        <v/>
+      </c>
+      <c r="U33" s="8">
+        <f>C33*$B$5*$B$16*S33/10^6</f>
+        <v/>
+      </c>
+      <c r="V33" s="8">
+        <f>SUM(T33:U33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Residual convolution 1</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>PosNet ResNet blocks 3–4</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10">
+        <f>E34*G34*H34/I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="11">
+        <f>C34*$B$5*J34/10^6</f>
+        <v/>
+      </c>
+      <c r="L34" s="10">
+        <f>J34+H34+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M34" s="10">
+        <f>C34*L34</f>
+        <v/>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="11">
+        <f>C34*N34/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q34" s="11">
+        <f>C34*O34/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R34" s="10">
+        <f>L34</f>
+        <v/>
+      </c>
+      <c r="S34" s="10">
+        <f>$B$17*(E34-1)*F34*G34+$B$18*(E34-1)*F34*G34</f>
+        <v/>
+      </c>
+      <c r="T34" s="11">
+        <f>C34*$B$5*$B$16*R34/10^6</f>
+        <v/>
+      </c>
+      <c r="U34" s="11">
+        <f>C34*$B$5*$B$16*S34/10^6</f>
+        <v/>
+      </c>
+      <c r="V34" s="11">
+        <f>SUM(T34:U34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Residual convolution 2</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>PosNet ResNet blocks 3–4</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10">
+        <f>E35*G35*H35/I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="11">
+        <f>C35*$B$5*J35/10^6</f>
+        <v/>
+      </c>
+      <c r="L35" s="10">
+        <f>J35+H35+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M35" s="10">
+        <f>C35*L35</f>
+        <v/>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <f>C35*N35/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q35" s="11">
+        <f>C35*O35/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R35" s="10">
+        <f>L35</f>
+        <v/>
+      </c>
+      <c r="S35" s="10">
+        <f>$B$17*(E35-1)*F35*G35+$B$18*(E35-1)*F35*G35</f>
+        <v/>
+      </c>
+      <c r="T35" s="11">
+        <f>C35*$B$5*$B$16*R35/10^6</f>
+        <v/>
+      </c>
+      <c r="U35" s="11">
+        <f>C35*$B$5*$B$16*S35/10^6</f>
+        <v/>
+      </c>
+      <c r="V35" s="11">
+        <f>SUM(T35:U35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Latent projection</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Encoder output</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H36" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7">
+        <f>E36*G36*H36/I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="8">
+        <f>C36*$B$5*J36/10^6</f>
+        <v/>
+      </c>
+      <c r="L36" s="7">
+        <f>J36+H36+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M36" s="7">
+        <f>C36*L36</f>
+        <v/>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8">
+        <f>C36*N36/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q36" s="8">
+        <f>C36*O36/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R36" s="7">
+        <f>L36</f>
+        <v/>
+      </c>
+      <c r="S36" s="7">
+        <f>$B$17*(E36-1)*F36*G36+$B$18*(E36-1)*F36*G36</f>
+        <v/>
+      </c>
+      <c r="T36" s="8">
+        <f>C36*$B$5*$B$16*R36/10^6</f>
+        <v/>
+      </c>
+      <c r="U36" s="8">
+        <f>C36*$B$5*$B$16*S36/10^6</f>
+        <v/>
+      </c>
+      <c r="V36" s="8">
+        <f>SUM(T36:U36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Formula-based total</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12">
-        <f>SUM(K18:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12">
-        <f>SUM(M18:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12">
-        <f>SUM(P18:P31)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="12">
-        <f>SUM(Q18:Q31)</f>
-        <v/>
-      </c>
-      <c r="R32" s="12">
-        <f>SUMPRODUCT(C18:C31,R18:R31)</f>
-        <v/>
-      </c>
-      <c r="S32" s="12" t="n"/>
-      <c r="T32" s="12">
-        <f>SUM(T18:T31)</f>
-        <v/>
-      </c>
-      <c r="U32" s="12">
-        <f>SUM(U18:U31)</f>
-        <v/>
-      </c>
-      <c r="V32" s="12">
-        <f>SUM(T32:U32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12">
+        <f>SUM(K20:K36)</f>
+        <v/>
+      </c>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12">
+        <f>SUM(M20:M36)</f>
+        <v/>
+      </c>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12">
+        <f>SUM(P20:P36)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="12">
+        <f>SUM(Q20:Q36)</f>
+        <v/>
+      </c>
+      <c r="R37" s="12">
+        <f>SUMPRODUCT(C20:C36,R20:R36)</f>
+        <v/>
+      </c>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="12">
+        <f>SUM(T20:T36)</f>
+        <v/>
+      </c>
+      <c r="U37" s="12">
+        <f>SUM(U20:U36)</f>
+        <v/>
+      </c>
+      <c r="V37" s="12">
+        <f>SUM(T37:U37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Total compute (MFLOPS)</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13">
-        <f>K32*2</f>
-        <v/>
-      </c>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="13" t="n"/>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="13" t="n"/>
-      <c r="R33" s="13" t="n"/>
-      <c r="S33" s="13" t="n"/>
-      <c r="T33" s="13" t="n"/>
-      <c r="U33" s="13" t="n"/>
-      <c r="V33" s="13" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Memory bandwidth uses the bytes-per-value setting in B14 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="13" t="n"/>
+      <c r="K38" s="13">
+        <f>K37*2</f>
+        <v/>
+      </c>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="13" t="n"/>
+      <c r="V38" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Memory bandwidth uses the bytes-per-value setting in B16 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
   </sheetData>
-  <autoFilter ref="A17:V31"/>
+  <autoFilter ref="A19:V36"/>
   <mergeCells count="3">
-    <mergeCell ref="D2:V16"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A35:V36"/>
+    <mergeCell ref="D2:V18"/>
+    <mergeCell ref="A40:V41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2357,7 +2645,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VoCodec DAC-Style RVQ Transmit — 100 Hz / 32-layer</t>
+          <t>VoCodec DAC-Style RVQ Transmit — 100 Hz / 24-layer / RoPE</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2708,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Maximum Bitrate (kbps)</t>
+          <t>Maximum Native Bitrate (kbps)</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -2481,7 +2769,7 @@
         <v>1024</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E4" s="6">
         <f>'Encoder-Track1'!$B$5</f>
@@ -2531,15 +2819,15 @@
         <v/>
       </c>
       <c r="Q4" s="6">
-        <f>E4*'Encoder-Track1'!$B$14*N4/10^6</f>
+        <f>E4*'Encoder-Track1'!$B$16*N4/10^6</f>
         <v/>
       </c>
       <c r="R4" s="6">
-        <f>E4*'Encoder-Track1'!$B$14*O4/10^6</f>
+        <f>E4*'Encoder-Track1'!$B$16*O4/10^6</f>
         <v/>
       </c>
       <c r="S4" s="6">
-        <f>E4*'Encoder-Track1'!$B$14*P4/10^6</f>
+        <f>E4*'Encoder-Track1'!$B$16*P4/10^6</f>
         <v/>
       </c>
       <c r="T4" s="6">
@@ -2556,7 +2844,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>The Track 1 baseline uses one factorized DAC RVQ: the low-dimensional codebooks and output projections are shared logical parameters and are counted once, while their transmit- and receive-side accesses are counted separately. An alternative deployment may keep the low-dimensional transmit codebooks and materialize separate receive codebooks containing the output-projected vectors. That alternative removes receive output-projection compute and parameter-read bandwidth. Under this sheet's MAC convention, receive VQ compute then becomes zero; receive VQ bandwidth becomes Frame Rate x Bytes per Value x RVQ Layers x Model Dimension, and the parameter cap gains RVQ Layers x Codebook Size x Model Dimension values for the materialized receive codebooks. Transmit accounting is unchanged. Those alternative values are not included here.</t>
+          <t>The Track 1 baseline uses one factorized DAC RVQ: the low-dimensional codebooks and output projections are shared logical parameters and are counted once, while their transmit- and receive-side accesses are counted separately. An alternative deployment may keep the low-dimensional transmit codebooks and materialize separate receive codebooks containing the output-projected vectors. That alternative removes receive output-projection compute and parameter-read bandwidth. Under this sheet's MAC convention, receive VQ compute then becomes zero; receive VQ bandwidth becomes Frame Rate x Bytes per Value x RVQ Layers x Model Dimension, and the parameter cap gains RVQ Layers x Codebook Size x Model Dimension values for the materialized receive codebooks. Transmit accounting is unchanged. Those alternative values are not included here. This design natively supports 1, 6, 12, 24 kbps. A request above 24 kbps, including 32 kbps, is clamped to all 24 layers and produces the same output as 24 kbps.</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2890,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VoCodec DAC-Style RVQ Receive — 100 Hz / 32-layer</t>
+          <t>VoCodec DAC-Style RVQ Receive — 100 Hz / 24-layer / RoPE</t>
         </is>
       </c>
     </row>
@@ -2737,11 +3025,11 @@
         <v/>
       </c>
       <c r="M4" s="6">
-        <f>E4*'Encoder-Track1'!$B$14*K4/10^6</f>
+        <f>E4*'Encoder-Track1'!$B$16*K4/10^6</f>
         <v/>
       </c>
       <c r="N4" s="6">
-        <f>E4*'Encoder-Track1'!$B$14*L4/10^6</f>
+        <f>E4*'Encoder-Track1'!$B$16*L4/10^6</f>
         <v/>
       </c>
       <c r="O4" s="6">
@@ -2758,7 +3046,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>The Track 1 baseline uses one factorized DAC RVQ: the low-dimensional codebooks and output projections are shared logical parameters and are counted once, while their transmit- and receive-side accesses are counted separately. An alternative deployment may keep the low-dimensional transmit codebooks and materialize separate receive codebooks containing the output-projected vectors. That alternative removes receive output-projection compute and parameter-read bandwidth. Under this sheet's MAC convention, receive VQ compute then becomes zero; receive VQ bandwidth becomes Frame Rate x Bytes per Value x RVQ Layers x Model Dimension, and the parameter cap gains RVQ Layers x Codebook Size x Model Dimension values for the materialized receive codebooks. Transmit accounting is unchanged. Those alternative values are not included here.</t>
+          <t>The Track 1 baseline uses one factorized DAC RVQ: the low-dimensional codebooks and output projections are shared logical parameters and are counted once, while their transmit- and receive-side accesses are counted separately. An alternative deployment may keep the low-dimensional transmit codebooks and materialize separate receive codebooks containing the output-projected vectors. That alternative removes receive output-projection compute and parameter-read bandwidth. Under this sheet's MAC convention, receive VQ compute then becomes zero; receive VQ bandwidth becomes Frame Rate x Bytes per Value x RVQ Layers x Model Dimension, and the parameter cap gains RVQ Layers x Codebook Size x Model Dimension values for the materialized receive codebooks. Transmit accounting is unchanged. Those alternative values are not included here. This design natively supports 1, 6, 12, 24 kbps. A request above 24 kbps, including 32 kbps, is clamped to all 24 layers and produces the same output as 24 kbps.</t>
         </is>
       </c>
     </row>
@@ -2780,7 +3068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -2810,7 +3098,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VoCodec Decoder — 100 Hz / 32-layer</t>
+          <t>VoCodec Decoder — 100 Hz / 24-layer / RoPE</t>
         </is>
       </c>
     </row>
@@ -2826,7 +3114,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Computations only include MAC-bearing operations. The first STFT/ISTFT row has zero counted MACs but explicitly accounts for its persistent window and streaming overlap state. LayerNorm arithmetic is omitted, while each LayerNorm's scale and bias values are included in column L through the +2*$B$6 terms; +4*$B$6 includes two LayerNorms. Hover over those cells for the exact association. Activations, residual additions, dropout, softmax, and FFT arithmetic are omitted under the LRAC sheet convention. Overall Stride in B5 drives compute, field-of-view, and memory-bandwidth formulas. Channel dimensions are centralized in B6:B9, and bounded attention settings are centralized in B10:B12. Bytes per value and runtime state read/write assumptions are centralized in B14:B16. The layer table references those cells. All totals derive only from visible formulas.</t>
+          <t>Computations only include MAC-bearing operations. The first STFT/ISTFT row has zero counted MACs but explicitly accounts for its persistent window and streaming overlap state. LayerNorm arithmetic is omitted, while each LayerNorm's scale and bias values are included in column L through the +2*$B$6 terms; +4*$B$6 includes two LayerNorms. Hover over those cells for the exact association. Activations, residual additions, dropout, softmax, and FFT arithmetic are omitted under the LRAC sheet convention. Overall Stride in B5 drives compute, field-of-view, and memory-bandwidth formulas. Channel dimensions are centralized in B6:B9, and bounded attention and RoPE settings are centralized in B10:B14. Bytes per value and runtime state read/write assumptions are centralized in B16:B18. The layer table references those cells. All totals derive only from visible formulas.</t>
         </is>
       </c>
     </row>
@@ -2881,7 +3169,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -2942,18 +3230,18 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ISTFT algorithmic latency (ms)</t>
+          <t>Attention uses RoPE</t>
         </is>
       </c>
       <c r="B13" s="3">
-        <f>($B$3-$B$4)/$B$2*1000</f>
+        <f>'Encoder-Track1'!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bytes per parameter/buffer value</t>
+          <t>RoPE rotary dimensions / head</t>
         </is>
       </c>
       <c r="B14" s="3">
@@ -2964,18 +3252,18 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Runtime state reads per call</t>
+          <t>ISTFT algorithmic latency (ms)</t>
         </is>
       </c>
       <c r="B15" s="3">
-        <f>'Encoder-Track1'!$B$15</f>
+        <f>($B$3-$B$4)/$B$2*1000</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Runtime state writes per call</t>
+          <t>Bytes per parameter/buffer value</t>
         </is>
       </c>
       <c r="B16" s="3">
@@ -2983,343 +3271,191 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Runtime state reads per call</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>'Encoder-Track1'!$B$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Runtime state writes per call</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>'Encoder-Track1'!$B$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Layer Name</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Block ID</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t># Blocks</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Operation</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Kernel / Context</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Dilation</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Input Channels</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Output Channels</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Groups / Heads</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>MAC / Position / Block</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>MMAC/s</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Trainable Params / Block</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Total Trainable Params</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>FOV Left / Block</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>FOV Right / Block</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Total FOV Left (ms)</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>Algorithmic Latency (ms)</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>Parameter-Cap Values / Block</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>Runtime State/Cache Accesses (R+W) / Call / Block</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>Model-Params BW Total (MB/s)</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>State/Cache BW Total (MB/s)</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>Total BW (MB/s)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ISTFT synthesis window and overlap state</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>ISTFT synthesis</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="C20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Persistent window and streaming state; FFT MACs excluded</t>
         </is>
       </c>
-      <c r="E18" s="6">
+      <c r="E20" s="6">
         <f>$B$3</f>
         <v/>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="8">
-        <f>C18*$B$5*J18/10^6</f>
-        <v/>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7">
-        <f>C18*L18</f>
-        <v/>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="8">
-        <f>C18*N18/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q18" s="8">
-        <f>C18*O18/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R18" s="7">
-        <f>$B$3</f>
-        <v/>
-      </c>
-      <c r="S18" s="7">
-        <f>$B$15*($B$3-$B$4)+$B$16*($B$3-$B$4)</f>
-        <v/>
-      </c>
-      <c r="T18" s="8">
-        <f>C18*$B$5*$B$14*R18/10^6</f>
-        <v/>
-      </c>
-      <c r="U18" s="8">
-        <f>C18*$B$5*$B$14*S18/10^6</f>
-        <v/>
-      </c>
-      <c r="V18" s="8">
-        <f>SUM(T18:U18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Latent projection</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Decoder input</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H19" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="10">
-        <f>E19*G19*H19/I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="11">
-        <f>C19*$B$5*J19/10^6</f>
-        <v/>
-      </c>
-      <c r="L19" s="10">
-        <f>J19+H19+0</f>
-        <v/>
-      </c>
-      <c r="M19" s="10">
-        <f>C19*L19</f>
-        <v/>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="11">
-        <f>C19*N19/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q19" s="11">
-        <f>C19*O19/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R19" s="10">
-        <f>L19</f>
-        <v/>
-      </c>
-      <c r="S19" s="10">
-        <f>$B$15*(E19-1)*F19*G19+$B$16*(E19-1)*F19*G19</f>
-        <v/>
-      </c>
-      <c r="T19" s="11">
-        <f>C19*$B$5*$B$14*R19/10^6</f>
-        <v/>
-      </c>
-      <c r="U19" s="11">
-        <f>C19*$B$5*$B$14*S19/10^6</f>
-        <v/>
-      </c>
-      <c r="V19" s="11">
-        <f>SUM(T19:U19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" outlineLevel="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Residual convolution 1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>PosNet ResNet blocks 1–2</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H20" s="6">
-        <f>$B$6</f>
-        <v/>
+      <c r="G20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="7">
-        <f>E20*G20*H20/I20</f>
-        <v/>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="8">
         <f>C20*$B$5*J20/10^6</f>
         <v/>
       </c>
-      <c r="L20" s="7">
-        <f>J20+H20+2*$B$6</f>
-        <v/>
+      <c r="L20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="7">
         <f>C20*L20</f>
         <v/>
       </c>
       <c r="N20" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>0</v>
@@ -3333,19 +3469,19 @@
         <v/>
       </c>
       <c r="R20" s="7">
-        <f>L20</f>
+        <f>$B$3</f>
         <v/>
       </c>
       <c r="S20" s="7">
-        <f>$B$15*(E20-1)*F20*G20+$B$16*(E20-1)*F20*G20</f>
+        <f>$B$17*($B$3-$B$4)+$B$18*($B$3-$B$4)</f>
         <v/>
       </c>
       <c r="T20" s="8">
-        <f>C20*$B$5*$B$14*R20/10^6</f>
+        <f>C20*$B$5*$B$16*R20/10^6</f>
         <v/>
       </c>
       <c r="U20" s="8">
-        <f>C20*$B$5*$B$14*S20/10^6</f>
+        <f>C20*$B$5*$B$16*S20/10^6</f>
         <v/>
       </c>
       <c r="V20" s="8">
@@ -3353,264 +3489,263 @@
         <v/>
       </c>
     </row>
-    <row r="21" outlineLevel="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Latent projection</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Decoder input</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10">
+        <f>E21*G21*H21/I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="11">
+        <f>C21*$B$5*J21/10^6</f>
+        <v/>
+      </c>
+      <c r="L21" s="10">
+        <f>J21+H21+0</f>
+        <v/>
+      </c>
+      <c r="M21" s="10">
+        <f>C21*L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="11">
+        <f>C21*N21/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q21" s="11">
+        <f>C21*O21/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R21" s="10">
+        <f>L21</f>
+        <v/>
+      </c>
+      <c r="S21" s="10">
+        <f>$B$17*(E21-1)*F21*G21+$B$18*(E21-1)*F21*G21</f>
+        <v/>
+      </c>
+      <c r="T21" s="11">
+        <f>C21*$B$5*$B$16*R21/10^6</f>
+        <v/>
+      </c>
+      <c r="U21" s="11">
+        <f>C21*$B$5*$B$16*S21/10^6</f>
+        <v/>
+      </c>
+      <c r="V21" s="11">
+        <f>SUM(T21:U21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Residual convolution 1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>PosNet ResNet blocks 1–2</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H22" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7">
+        <f>E22*G22*H22/I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="8">
+        <f>C22*$B$5*J22/10^6</f>
+        <v/>
+      </c>
+      <c r="L22" s="7">
+        <f>J22+H22+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M22" s="7">
+        <f>C22*L22</f>
+        <v/>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8">
+        <f>C22*N22/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q22" s="8">
+        <f>C22*O22/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R22" s="7">
+        <f>L22</f>
+        <v/>
+      </c>
+      <c r="S22" s="7">
+        <f>$B$17*(E22-1)*F22*G22+$B$18*(E22-1)*F22*G22</f>
+        <v/>
+      </c>
+      <c r="T22" s="8">
+        <f>C22*$B$5*$B$16*R22/10^6</f>
+        <v/>
+      </c>
+      <c r="U22" s="8">
+        <f>C22*$B$5*$B$16*S22/10^6</f>
+        <v/>
+      </c>
+      <c r="V22" s="8">
+        <f>SUM(T22:U22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Residual convolution 2</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PosNet ResNet blocks 1–2</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Causal Conv1d</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H21" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="7">
-        <f>E21*G21*H21/I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="8">
-        <f>C21*$B$5*J21/10^6</f>
-        <v/>
-      </c>
-      <c r="L21" s="7">
-        <f>J21+H21+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M21" s="7">
-        <f>C21*L21</f>
-        <v/>
-      </c>
-      <c r="N21" s="6" t="n">
+      <c r="F23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H23" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7">
+        <f>E23*G23*H23/I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="8">
+        <f>C23*$B$5*J23/10^6</f>
+        <v/>
+      </c>
+      <c r="L23" s="7">
+        <f>J23+H23+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>C23*L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="O21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8">
-        <f>C21*N21/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q21" s="8">
-        <f>C21*O21/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R21" s="7">
-        <f>L21</f>
-        <v/>
-      </c>
-      <c r="S21" s="7">
-        <f>$B$15*(E21-1)*F21*G21+$B$16*(E21-1)*F21*G21</f>
-        <v/>
-      </c>
-      <c r="T21" s="8">
-        <f>C21*$B$5*$B$14*R21/10^6</f>
-        <v/>
-      </c>
-      <c r="U21" s="8">
-        <f>C21*$B$5*$B$14*S21/10^6</f>
-        <v/>
-      </c>
-      <c r="V21" s="8">
-        <f>SUM(T21:U21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>QKV projection</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Bounded attention after PosNet block 2</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Conv1d / linear projection</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H22" s="9">
-        <f>$B$8</f>
-        <v/>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="10">
-        <f>E22*G22*H22/I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="11">
-        <f>C22*$B$5*J22/10^6</f>
-        <v/>
-      </c>
-      <c r="L22" s="10">
-        <f>J22+H22+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M22" s="10">
-        <f>C22*L22</f>
-        <v/>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="11">
-        <f>C22*N22/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="Q22" s="11">
-        <f>C22*O22/$B$5*1000</f>
-        <v/>
-      </c>
-      <c r="R22" s="10">
-        <f>L22</f>
-        <v/>
-      </c>
-      <c r="S22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="11">
-        <f>C22*$B$5*$B$14*R22/10^6</f>
-        <v/>
-      </c>
-      <c r="U22" s="11">
-        <f>C22*$B$5*$B$14*S22/10^6</f>
-        <v/>
-      </c>
-      <c r="V22" s="11">
-        <f>SUM(T22:U22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Query-key score product</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Bounded attention after PosNet block 2</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Q × Kᵀ (configured bounded context)</t>
-        </is>
-      </c>
-      <c r="E23" s="9">
-        <f>$B$10+$B$11</f>
-        <v/>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>$B$12</f>
-        <v/>
-      </c>
-      <c r="J23" s="10">
-        <f>I23*E23*(G23/I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="11">
-        <f>C23*$B$5*J23/10^6</f>
-        <v/>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="10">
-        <f>C23*L23</f>
-        <v/>
-      </c>
-      <c r="N23" s="9">
-        <f>$B$10-1</f>
-        <v/>
-      </c>
-      <c r="O23" s="9">
-        <f>$B$11</f>
-        <v/>
-      </c>
-      <c r="P23" s="11">
+      <c r="O23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8">
         <f>C23*N23/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q23" s="11">
+      <c r="Q23" s="8">
         <f>C23*O23/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="10">
-        <f>$B$15*($B$10-1+$B$11)*G23+$B$16*G23</f>
-        <v/>
-      </c>
-      <c r="T23" s="11">
-        <f>C23*$B$5*$B$14*R23/10^6</f>
-        <v/>
-      </c>
-      <c r="U23" s="11">
-        <f>C23*$B$5*$B$14*S23/10^6</f>
-        <v/>
-      </c>
-      <c r="V23" s="11">
+      <c r="R23" s="7">
+        <f>L23</f>
+        <v/>
+      </c>
+      <c r="S23" s="7">
+        <f>$B$17*(E23-1)*F23*G23+$B$18*(E23-1)*F23*G23</f>
+        <v/>
+      </c>
+      <c r="T23" s="8">
+        <f>C23*$B$5*$B$16*R23/10^6</f>
+        <v/>
+      </c>
+      <c r="U23" s="8">
+        <f>C23*$B$5*$B$16*S23/10^6</f>
+        <v/>
+      </c>
+      <c r="V23" s="8">
         <f>SUM(T23:U23)</f>
         <v/>
       </c>
@@ -3618,7 +3753,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Attention-weighted value product</t>
+          <t>QKV projection</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -3631,12 +3766,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>softmax(QKᵀ) × V</t>
-        </is>
-      </c>
-      <c r="E24" s="9">
-        <f>$B$10+$B$11</f>
-        <v/>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1</v>
@@ -3646,23 +3780,23 @@
         <v/>
       </c>
       <c r="H24" s="9">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I24" s="9">
-        <f>$B$12</f>
-        <v/>
+        <f>$B$8</f>
+        <v/>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="J24" s="10">
-        <f>I24*E24*(G24/I24)</f>
+        <f>E24*G24*H24/I24</f>
         <v/>
       </c>
       <c r="K24" s="11">
         <f>C24*$B$5*J24/10^6</f>
         <v/>
       </c>
-      <c r="L24" s="10" t="n">
-        <v>0</v>
+      <c r="L24" s="10">
+        <f>J24+H24+2*$B$6</f>
+        <v/>
       </c>
       <c r="M24" s="10">
         <f>C24*L24</f>
@@ -3682,19 +3816,19 @@
         <f>C24*O24/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="10">
-        <f>$B$15*($B$10-1+$B$11)*G24+$B$16*G24</f>
-        <v/>
+      <c r="R24" s="10">
+        <f>L24</f>
+        <v/>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="T24" s="11">
-        <f>C24*$B$5*$B$14*R24/10^6</f>
+        <f>C24*$B$5*$B$16*R24/10^6</f>
         <v/>
       </c>
       <c r="U24" s="11">
-        <f>C24*$B$5*$B$14*S24/10^6</f>
+        <f>C24*$B$5*$B$16*S24/10^6</f>
         <v/>
       </c>
       <c r="V24" s="11">
@@ -3705,7 +3839,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Attention output projection</t>
+          <t>RoPE phase generation</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -3718,11 +3852,12 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Conv1d / linear projection</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>1</v>
+          <t>Position × derived inverse frequencies; sine/cosine arithmetic excluded</t>
+        </is>
+      </c>
+      <c r="E25" s="9">
+        <f>$B$14/2</f>
+        <v/>
       </c>
       <c r="F25" s="9" t="n">
         <v>1</v>
@@ -3739,16 +3874,15 @@
         <v>1</v>
       </c>
       <c r="J25" s="10">
-        <f>E25*G25*H25/I25</f>
+        <f>E25</f>
         <v/>
       </c>
       <c r="K25" s="11">
         <f>C25*$B$5*J25/10^6</f>
         <v/>
       </c>
-      <c r="L25" s="10">
-        <f>J25+H25+0</f>
-        <v/>
+      <c r="L25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="10">
         <f>C25*L25</f>
@@ -3768,19 +3902,19 @@
         <f>C25*O25/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R25" s="10">
-        <f>L25</f>
-        <v/>
-      </c>
-      <c r="S25" s="10" t="n">
-        <v>0</v>
+      <c r="R25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="10">
+        <f>$B$17*($B$14/2)</f>
+        <v/>
       </c>
       <c r="T25" s="11">
-        <f>C25*$B$5*$B$14*R25/10^6</f>
+        <f>C25*$B$5*$B$16*R25/10^6</f>
         <v/>
       </c>
       <c r="U25" s="11">
-        <f>C25*$B$5*$B$14*S25/10^6</f>
+        <f>C25*$B$5*$B$16*S25/10^6</f>
         <v/>
       </c>
       <c r="V25" s="11">
@@ -3788,201 +3922,200 @@
         <v/>
       </c>
     </row>
-    <row r="26" outlineLevel="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Residual convolution 1</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>PosNet ResNet blocks 3–4</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H26" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="7">
-        <f>E26*G26*H26/I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="8">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>RoPE query rotation</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Bounded attention after PosNet block 2</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Pairwise rotary transform of Q</t>
+        </is>
+      </c>
+      <c r="E26" s="9">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I26" s="9">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="J26" s="10">
+        <f>2*E26*I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="11">
         <f>C26*$B$5*J26/10^6</f>
         <v/>
       </c>
-      <c r="L26" s="7">
-        <f>J26+H26+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M26" s="7">
+      <c r="L26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10">
         <f>C26*L26</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8">
+      <c r="N26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="11">
         <f>C26*N26/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q26" s="8">
+      <c r="Q26" s="11">
         <f>C26*O26/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R26" s="7">
-        <f>L26</f>
-        <v/>
-      </c>
-      <c r="S26" s="7">
-        <f>$B$15*(E26-1)*F26*G26+$B$16*(E26-1)*F26*G26</f>
-        <v/>
-      </c>
-      <c r="T26" s="8">
-        <f>C26*$B$5*$B$14*R26/10^6</f>
-        <v/>
-      </c>
-      <c r="U26" s="8">
-        <f>C26*$B$5*$B$14*S26/10^6</f>
-        <v/>
-      </c>
-      <c r="V26" s="8">
+      <c r="R26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="11">
+        <f>C26*$B$5*$B$16*R26/10^6</f>
+        <v/>
+      </c>
+      <c r="U26" s="11">
+        <f>C26*$B$5*$B$16*S26/10^6</f>
+        <v/>
+      </c>
+      <c r="V26" s="11">
         <f>SUM(T26:U26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" outlineLevel="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Residual convolution 2</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>PosNet ResNet blocks 3–4</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="H27" s="6">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="7">
-        <f>E27*G27*H27/I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="8">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>RoPE key rotation</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Bounded attention after PosNet block 2</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Pairwise rotary transform of K before cache use</t>
+        </is>
+      </c>
+      <c r="E27" s="9">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I27" s="9">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="J27" s="10">
+        <f>2*E27*I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="11">
         <f>C27*$B$5*J27/10^6</f>
         <v/>
       </c>
-      <c r="L27" s="7">
-        <f>J27+H27+2*$B$6</f>
-        <v/>
-      </c>
-      <c r="M27" s="7">
+      <c r="L27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10">
         <f>C27*L27</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="8">
+      <c r="N27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="11">
         <f>C27*N27/$B$5*1000</f>
         <v/>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="11">
         <f>C27*O27/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R27" s="7">
-        <f>L27</f>
-        <v/>
-      </c>
-      <c r="S27" s="7">
-        <f>$B$15*(E27-1)*F27*G27+$B$16*(E27-1)*F27*G27</f>
-        <v/>
-      </c>
-      <c r="T27" s="8">
-        <f>C27*$B$5*$B$14*R27/10^6</f>
-        <v/>
-      </c>
-      <c r="U27" s="8">
-        <f>C27*$B$5*$B$14*S27/10^6</f>
-        <v/>
-      </c>
-      <c r="V27" s="8">
+      <c r="R27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="11">
+        <f>C27*$B$5*$B$16*R27/10^6</f>
+        <v/>
+      </c>
+      <c r="U27" s="11">
+        <f>C27*$B$5*$B$16*S27/10^6</f>
+        <v/>
+      </c>
+      <c r="V27" s="11">
         <f>SUM(T27:U27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" outlineLevel="1">
+    <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Depthwise convolution</t>
+          <t>Query-key score product</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>ConvNeXt blocks 1–6</t>
+          <t>Bounded attention after PosNet block 2</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Causal Conv1d</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>7</v>
+          <t>Q × Kᵀ (configured bounded context)</t>
+        </is>
+      </c>
+      <c r="E28" s="9">
+        <f>$B$10+$B$11</f>
+        <v/>
       </c>
       <c r="F28" s="9" t="n">
         <v>1</v>
@@ -3996,30 +4129,31 @@
         <v/>
       </c>
       <c r="I28" s="9">
-        <f>$B$6</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="J28" s="10">
-        <f>E28*G28*H28/I28</f>
+        <f>I28*E28*(G28/I28)</f>
         <v/>
       </c>
       <c r="K28" s="11">
         <f>C28*$B$5*J28/10^6</f>
         <v/>
       </c>
-      <c r="L28" s="10">
-        <f>J28+H28+2*$B$6</f>
-        <v/>
+      <c r="L28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="10">
         <f>C28*L28</f>
         <v/>
       </c>
-      <c r="N28" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O28" s="9" t="n">
-        <v>0</v>
+      <c r="N28" s="9">
+        <f>$B$10-1</f>
+        <v/>
+      </c>
+      <c r="O28" s="9">
+        <f>$B$11</f>
+        <v/>
       </c>
       <c r="P28" s="11">
         <f>C28*N28/$B$5*1000</f>
@@ -4029,20 +4163,19 @@
         <f>C28*O28/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R28" s="10">
-        <f>L28</f>
-        <v/>
+      <c r="R28" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="S28" s="10">
-        <f>$B$15*(E28-1)*F28*G28+$B$16*(E28-1)*F28*G28</f>
+        <f>$B$17*($B$10-1+$B$11)*G28+$B$18*G28</f>
         <v/>
       </c>
       <c r="T28" s="11">
-        <f>C28*$B$5*$B$14*R28/10^6</f>
+        <f>C28*$B$5*$B$16*R28/10^6</f>
         <v/>
       </c>
       <c r="U28" s="11">
-        <f>C28*$B$5*$B$14*S28/10^6</f>
+        <f>C28*$B$5*$B$16*S28/10^6</f>
         <v/>
       </c>
       <c r="V28" s="11">
@@ -4050,27 +4183,28 @@
         <v/>
       </c>
     </row>
-    <row r="29" outlineLevel="1">
+    <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Pointwise input projection</t>
+          <t>Attention-weighted value product</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>ConvNeXt blocks 1–6</t>
+          <t>Bounded attention after PosNet block 2</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Conv1d / linear projection</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>1</v>
+          <t>softmax(QKᵀ) × V</t>
+        </is>
+      </c>
+      <c r="E29" s="9">
+        <f>$B$10+$B$11</f>
+        <v/>
       </c>
       <c r="F29" s="9" t="n">
         <v>1</v>
@@ -4080,23 +4214,23 @@
         <v/>
       </c>
       <c r="H29" s="9">
-        <f>$B$7</f>
-        <v/>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>1</v>
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>$B$12</f>
+        <v/>
       </c>
       <c r="J29" s="10">
-        <f>E29*G29*H29/I29</f>
+        <f>I29*E29*(G29/I29)</f>
         <v/>
       </c>
       <c r="K29" s="11">
         <f>C29*$B$5*J29/10^6</f>
         <v/>
       </c>
-      <c r="L29" s="10">
-        <f>J29+H29+0</f>
-        <v/>
+      <c r="L29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="10">
         <f>C29*L29</f>
@@ -4116,19 +4250,19 @@
         <f>C29*O29/$B$5*1000</f>
         <v/>
       </c>
-      <c r="R29" s="10">
-        <f>L29</f>
-        <v/>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>0</v>
+      <c r="R29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="10">
+        <f>$B$17*($B$10-1+$B$11)*G29+$B$18*G29</f>
+        <v/>
       </c>
       <c r="T29" s="11">
-        <f>C29*$B$5*$B$14*R29/10^6</f>
+        <f>C29*$B$5*$B$16*R29/10^6</f>
         <v/>
       </c>
       <c r="U29" s="11">
-        <f>C29*$B$5*$B$14*S29/10^6</f>
+        <f>C29*$B$5*$B$16*S29/10^6</f>
         <v/>
       </c>
       <c r="V29" s="11">
@@ -4136,19 +4270,19 @@
         <v/>
       </c>
     </row>
-    <row r="30" outlineLevel="1">
+    <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Pointwise output projection</t>
+          <t>Attention output projection</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>ConvNeXt blocks 1–6</t>
+          <t>Bounded attention after PosNet block 2</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
@@ -4162,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="9">
-        <f>$B$7</f>
+        <f>$B$6</f>
         <v/>
       </c>
       <c r="H30" s="9">
@@ -4210,11 +4344,11 @@
         <v>0</v>
       </c>
       <c r="T30" s="11">
-        <f>C30*$B$5*$B$14*R30/10^6</f>
+        <f>C30*$B$5*$B$16*R30/10^6</f>
         <v/>
       </c>
       <c r="U30" s="11">
-        <f>C30*$B$5*$B$14*S30/10^6</f>
+        <f>C30*$B$5*$B$16*S30/10^6</f>
         <v/>
       </c>
       <c r="V30" s="11">
@@ -4222,27 +4356,27 @@
         <v/>
       </c>
     </row>
-    <row r="31">
+    <row r="31" outlineLevel="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Complex-spectrum output projection</t>
+          <t>Residual convolution 1</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Decoder output</t>
+          <t>PosNet ResNet blocks 3–4</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Conv1d / linear projection</t>
+          <t>Causal Conv1d</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>1</v>
@@ -4252,11 +4386,11 @@
         <v/>
       </c>
       <c r="H31" s="6">
-        <f>$B$9</f>
+        <f>$B$6</f>
         <v/>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="7">
         <f>E31*G31*H31/I31</f>
@@ -4267,7 +4401,7 @@
         <v/>
       </c>
       <c r="L31" s="7">
-        <f>J31+H31+4*$B$6</f>
+        <f>J31+H31+2*$B$6</f>
         <v/>
       </c>
       <c r="M31" s="7">
@@ -4275,7 +4409,7 @@
         <v/>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="6" t="n">
         <v>0</v>
@@ -4292,15 +4426,16 @@
         <f>L31</f>
         <v/>
       </c>
-      <c r="S31" s="7" t="n">
-        <v>0</v>
+      <c r="S31" s="7">
+        <f>$B$17*(E31-1)*F31*G31+$B$18*(E31-1)*F31*G31</f>
+        <v/>
       </c>
       <c r="T31" s="8">
-        <f>C31*$B$5*$B$14*R31/10^6</f>
+        <f>C31*$B$5*$B$16*R31/10^6</f>
         <v/>
       </c>
       <c r="U31" s="8">
-        <f>C31*$B$5*$B$14*S31/10^6</f>
+        <f>C31*$B$5*$B$16*S31/10^6</f>
         <v/>
       </c>
       <c r="V31" s="8">
@@ -4308,103 +4443,536 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="32" outlineLevel="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Residual convolution 2</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>PosNet ResNet blocks 3–4</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H32" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="7">
+        <f>E32*G32*H32/I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="8">
+        <f>C32*$B$5*J32/10^6</f>
+        <v/>
+      </c>
+      <c r="L32" s="7">
+        <f>J32+H32+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M32" s="7">
+        <f>C32*L32</f>
+        <v/>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <f>C32*N32/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q32" s="8">
+        <f>C32*O32/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R32" s="7">
+        <f>L32</f>
+        <v/>
+      </c>
+      <c r="S32" s="7">
+        <f>$B$17*(E32-1)*F32*G32+$B$18*(E32-1)*F32*G32</f>
+        <v/>
+      </c>
+      <c r="T32" s="8">
+        <f>C32*$B$5*$B$16*R32/10^6</f>
+        <v/>
+      </c>
+      <c r="U32" s="8">
+        <f>C32*$B$5*$B$16*S32/10^6</f>
+        <v/>
+      </c>
+      <c r="V32" s="8">
+        <f>SUM(T32:U32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Depthwise convolution</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>ConvNeXt blocks 1–6</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Causal Conv1d</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H33" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I33" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="J33" s="10">
+        <f>E33*G33*H33/I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="11">
+        <f>C33*$B$5*J33/10^6</f>
+        <v/>
+      </c>
+      <c r="L33" s="10">
+        <f>J33+H33+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="M33" s="10">
+        <f>C33*L33</f>
+        <v/>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="11">
+        <f>C33*N33/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q33" s="11">
+        <f>C33*O33/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R33" s="10">
+        <f>L33</f>
+        <v/>
+      </c>
+      <c r="S33" s="10">
+        <f>$B$17*(E33-1)*F33*G33+$B$18*(E33-1)*F33*G33</f>
+        <v/>
+      </c>
+      <c r="T33" s="11">
+        <f>C33*$B$5*$B$16*R33/10^6</f>
+        <v/>
+      </c>
+      <c r="U33" s="11">
+        <f>C33*$B$5*$B$16*S33/10^6</f>
+        <v/>
+      </c>
+      <c r="V33" s="11">
+        <f>SUM(T33:U33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Pointwise input projection</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>ConvNeXt blocks 1–6</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10">
+        <f>E34*G34*H34/I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="11">
+        <f>C34*$B$5*J34/10^6</f>
+        <v/>
+      </c>
+      <c r="L34" s="10">
+        <f>J34+H34+0</f>
+        <v/>
+      </c>
+      <c r="M34" s="10">
+        <f>C34*L34</f>
+        <v/>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="11">
+        <f>C34*N34/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q34" s="11">
+        <f>C34*O34/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R34" s="10">
+        <f>L34</f>
+        <v/>
+      </c>
+      <c r="S34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="11">
+        <f>C34*$B$5*$B$16*R34/10^6</f>
+        <v/>
+      </c>
+      <c r="U34" s="11">
+        <f>C34*$B$5*$B$16*S34/10^6</f>
+        <v/>
+      </c>
+      <c r="V34" s="11">
+        <f>SUM(T34:U34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Pointwise output projection</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>ConvNeXt blocks 1–6</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9">
+        <f>$B$7</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10">
+        <f>E35*G35*H35/I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="11">
+        <f>C35*$B$5*J35/10^6</f>
+        <v/>
+      </c>
+      <c r="L35" s="10">
+        <f>J35+H35+0</f>
+        <v/>
+      </c>
+      <c r="M35" s="10">
+        <f>C35*L35</f>
+        <v/>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <f>C35*N35/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q35" s="11">
+        <f>C35*O35/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R35" s="10">
+        <f>L35</f>
+        <v/>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="11">
+        <f>C35*$B$5*$B$16*R35/10^6</f>
+        <v/>
+      </c>
+      <c r="U35" s="11">
+        <f>C35*$B$5*$B$16*S35/10^6</f>
+        <v/>
+      </c>
+      <c r="V35" s="11">
+        <f>SUM(T35:U35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Complex-spectrum output projection</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Decoder output</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Conv1d / linear projection</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H36" s="6">
+        <f>$B$9</f>
+        <v/>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7">
+        <f>E36*G36*H36/I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="8">
+        <f>C36*$B$5*J36/10^6</f>
+        <v/>
+      </c>
+      <c r="L36" s="7">
+        <f>J36+H36+4*$B$6</f>
+        <v/>
+      </c>
+      <c r="M36" s="7">
+        <f>C36*L36</f>
+        <v/>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8">
+        <f>C36*N36/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="Q36" s="8">
+        <f>C36*O36/$B$5*1000</f>
+        <v/>
+      </c>
+      <c r="R36" s="7">
+        <f>L36</f>
+        <v/>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="8">
+        <f>C36*$B$5*$B$16*R36/10^6</f>
+        <v/>
+      </c>
+      <c r="U36" s="8">
+        <f>C36*$B$5*$B$16*S36/10^6</f>
+        <v/>
+      </c>
+      <c r="V36" s="8">
+        <f>SUM(T36:U36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Formula-based total</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12">
-        <f>SUM(K18:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12">
-        <f>SUM(M18:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12">
-        <f>SUM(P18:P31)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="12">
-        <f>SUM(Q18:Q31)+$B$13</f>
-        <v/>
-      </c>
-      <c r="R32" s="12">
-        <f>SUMPRODUCT(C18:C31,R18:R31)</f>
-        <v/>
-      </c>
-      <c r="S32" s="12" t="n"/>
-      <c r="T32" s="12">
-        <f>SUM(T18:T31)</f>
-        <v/>
-      </c>
-      <c r="U32" s="12">
-        <f>SUM(U18:U31)</f>
-        <v/>
-      </c>
-      <c r="V32" s="12">
-        <f>SUM(T32:U32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12">
+        <f>SUM(K20:K36)</f>
+        <v/>
+      </c>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12">
+        <f>SUM(M20:M36)</f>
+        <v/>
+      </c>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12">
+        <f>SUM(P20:P36)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="12">
+        <f>SUM(Q20:Q36)+$B$15</f>
+        <v/>
+      </c>
+      <c r="R37" s="12">
+        <f>SUMPRODUCT(C20:C36,R20:R36)</f>
+        <v/>
+      </c>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="12">
+        <f>SUM(T20:T36)</f>
+        <v/>
+      </c>
+      <c r="U37" s="12">
+        <f>SUM(U20:U36)</f>
+        <v/>
+      </c>
+      <c r="V37" s="12">
+        <f>SUM(T37:U37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Total compute (MFLOPS)</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13">
-        <f>K32*2</f>
-        <v/>
-      </c>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="13" t="n"/>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="13" t="n"/>
-      <c r="R33" s="13" t="n"/>
-      <c r="S33" s="13" t="n"/>
-      <c r="T33" s="13" t="n"/>
-      <c r="U33" s="13" t="n"/>
-      <c r="V33" s="13" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Memory bandwidth uses the bytes-per-value setting in B14 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="13" t="n"/>
+      <c r="K38" s="13">
+        <f>K37*2</f>
+        <v/>
+      </c>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="n"/>
+      <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="13" t="n"/>
+      <c r="V38" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Memory bandwidth uses the bytes-per-value setting in B16 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
   </sheetData>
-  <autoFilter ref="A17:V31"/>
+  <autoFilter ref="A19:V36"/>
   <mergeCells count="3">
-    <mergeCell ref="D2:V16"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A35:V36"/>
+    <mergeCell ref="D2:V18"/>
+    <mergeCell ref="A40:V41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4431,7 +4999,7 @@
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VoCodec LRAC 2 Track 1 Summary — 100 Hz / 32-layer</t>
+          <t>VoCodec LRAC 2 Track 1 Summary — 100 Hz / 24-layer / RoPE</t>
         </is>
       </c>
     </row>
@@ -4469,7 +5037,7 @@
         </is>
       </c>
       <c r="B4" s="9">
-        <f>'Encoder-Track1'!K32*2+'VQ-Transmit-Track1'!I4</f>
+        <f>'Encoder-Track1'!K37*2+'VQ-Transmit-Track1'!I4</f>
         <v/>
       </c>
       <c r="C4" s="9" t="n">
@@ -4491,7 +5059,7 @@
         </is>
       </c>
       <c r="B5" s="9">
-        <f>'VQ-Receive-Track1'!G4+'Decoder-Track1'!K32*2</f>
+        <f>'VQ-Receive-Track1'!G4+'Decoder-Track1'!K37*2</f>
         <v/>
       </c>
       <c r="C5" s="9" t="n">
@@ -4513,7 +5081,7 @@
         </is>
       </c>
       <c r="B6" s="9">
-        <f>'Encoder-Track1'!$B$13</f>
+        <f>'Encoder-Track1'!$B$15</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr"/>
@@ -4527,7 +5095,7 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>'Encoder-Track1'!Q32+'Decoder-Track1'!Q32</f>
+        <f>'Encoder-Track1'!Q37+'Decoder-Track1'!Q37</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
@@ -4559,7 +5127,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Maximum bitrate (kbps)</t>
+          <t>Maximum native bitrate (kbps)</t>
         </is>
       </c>
       <c r="B9" s="9">
@@ -4577,7 +5145,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>'Encoder-Track1'!M32+'VQ-Transmit-Track1'!K4+'Decoder-Track1'!M32</f>
+        <f>'Encoder-Track1'!M37+'VQ-Transmit-Track1'!K4+'Decoder-Track1'!M37</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr"/>
@@ -4591,7 +5159,7 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>'Encoder-Track1'!R32+'VQ-Transmit-Track1'!K4+'Decoder-Track1'!R32</f>
+        <f>'Encoder-Track1'!R37+'VQ-Transmit-Track1'!K4+'Decoder-Track1'!R37</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr"/>
@@ -4612,7 +5180,7 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>'Encoder-Track1'!V32</f>
+        <f>'Encoder-Track1'!V37</f>
         <v/>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -4654,7 +5222,7 @@
         </is>
       </c>
       <c r="B17" s="11">
-        <f>'Decoder-Track1'!V32</f>
+        <f>'Decoder-Track1'!V37</f>
         <v/>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -4705,7 +5273,7 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>The 100 Hz / 32-layer design meets the transmitter compute, receiver compute, and total-latency Track 1 limits. Memory bandwidth includes encoder, maximum-rate RVQ transmit and receive paths, and decoder.</t>
+          <t>The 100 Hz / 24-layer / RoPE design meets the transmitter compute, receiver compute, and total-latency Track 1 limits. Memory bandwidth includes encoder, maximum-native-rate RVQ transmit and receive paths, and decoder. Requests above 24 kbps are clamped to the maximum native RVQ prefix.</t>
         </is>
       </c>
     </row>

--- a/egs2/lrac2/track1/LRAC2-Track1-VoCodec-Model-Design-Sheet.xlsx
+++ b/egs2/lrac2/track1/LRAC2-Track1-VoCodec-Model-Design-Sheet.xlsx
@@ -885,7 +885,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>STFT buffering latency (ms)</t>
+          <t>Frame-hop buffering latency (ms)</t>
         </is>
       </c>
       <c r="B15" s="3">
@@ -1084,18 +1084,20 @@
         <f>C20*L20</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>0</v>
+      <c r="N20" s="6">
+        <f>($B$3-$B$4)/2</f>
+        <v/>
+      </c>
+      <c r="O20" s="6">
+        <f>($B$3-$B$4)/2</f>
+        <v/>
       </c>
       <c r="P20" s="8">
-        <f>C20*N20/$B$5*1000</f>
+        <f>C20*N20/$B$2*1000</f>
         <v/>
       </c>
       <c r="Q20" s="8">
-        <f>C20*O20/$B$5*1000</f>
+        <f>C20*O20/$B$2*1000</f>
         <v/>
       </c>
       <c r="R20" s="7">
@@ -2592,7 +2594,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Memory bandwidth uses the bytes-per-value setting in B16 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
+          <t>Memory bandwidth uses the bytes-per-value setting in B16 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT frames use centred hop alignment and have (FFT size - hop) / 2 samples of left and right context. Their overlap state remains FFT size - hop samples. Window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
         </is>
       </c>
     </row>
@@ -3252,11 +3254,11 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ISTFT algorithmic latency (ms)</t>
+          <t>ISTFT synthesis lookahead (ms)</t>
         </is>
       </c>
       <c r="B15" s="3">
-        <f>($B$3-$B$4)/$B$2*1000</f>
+        <f>(($B$3-$B$4)/2)/$B$2*1000</f>
         <v/>
       </c>
     </row>
@@ -3454,18 +3456,20 @@
         <f>C20*L20</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>0</v>
+      <c r="N20" s="6">
+        <f>($B$3-$B$4)/2</f>
+        <v/>
+      </c>
+      <c r="O20" s="6">
+        <f>($B$3-$B$4)/2</f>
+        <v/>
       </c>
       <c r="P20" s="8">
-        <f>C20*N20/$B$5*1000</f>
+        <f>C20*N20/$B$2*1000</f>
         <v/>
       </c>
       <c r="Q20" s="8">
-        <f>C20*O20/$B$5*1000</f>
+        <f>C20*O20/$B$2*1000</f>
         <v/>
       </c>
       <c r="R20" s="7">
@@ -4907,7 +4911,7 @@
         <v/>
       </c>
       <c r="Q37" s="12">
-        <f>SUM(Q20:Q36)+$B$15</f>
+        <f>SUM(Q20:Q36)</f>
         <v/>
       </c>
       <c r="R37" s="12">
@@ -4962,7 +4966,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Memory bandwidth uses the bytes-per-value setting in B16 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
+          <t>Memory bandwidth uses the bytes-per-value setting in B16 and includes model parameters, model buffers, convolution state, and attention KV-cache. Parameter-cap values include trainable parameters and non-runtime model buffers required for inference. Runtime state/cache is excluded from the parameter cap, but its read/write traffic is included in memory bandwidth. Intermediate activations are excluded by the challenge convention. Attention MACs assume that the configured context buffer is fully populated; startup frames require less compute. FOV left is history, not latency; only FOV right contributes to algorithmic latency. STFT/ISTFT frames use centred hop alignment and have (FFT size - hop) / 2 samples of left and right context. Their overlap state remains FFT size - hop samples. Window and overlap-state bandwidth is shown explicitly in the first table row; FFT arithmetic is excluded.</t>
         </is>
       </c>
     </row>
